--- a/ingress-workflow_examples/animal/OpenField/result/rectangle.xlsx
+++ b/ingress-workflow_examples/animal/OpenField/result/rectangle.xlsx
@@ -755,121 +755,121 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.148274673856886</v>
+        <v>5.31971484802526</v>
       </c>
       <c r="C4" t="n">
-        <v>0.124729528151553</v>
+        <v>0.07424310456051998</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04613531040316703</v>
+        <v>0.02715588677028999</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>65.2</v>
+        <v>130.4</v>
       </c>
       <c r="H4" t="n">
-        <v>71.1691738475746</v>
+        <v>77.57101447043691</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1629418135380637</v>
+        <v>0.07676318068385336</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05971565337473349</v>
+        <v>0.03302913368416506</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M4" t="n">
-        <v>397.3666666666667</v>
+        <v>794.7333333333333</v>
       </c>
       <c r="N4" t="n">
-        <v>23.01600614961761</v>
+        <v>25.42619625243019</v>
       </c>
       <c r="O4" t="n">
-        <v>0.144737367235054</v>
+        <v>0.07345622190158614</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09176091622943369</v>
+        <v>0.03226511696987081</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="S4" t="n">
-        <v>137.1</v>
+        <v>274.2</v>
       </c>
       <c r="T4" t="n">
-        <v>15.04008299203686</v>
+        <v>18.2117629646571</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1524419999843377</v>
+        <v>0.07223400452953403</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06243659347415476</v>
+        <v>0.0317204773454373</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="Y4" t="n">
-        <v>111.4</v>
+        <v>222.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.76055707466713</v>
+        <v>18.39027093326664</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1584507047168379</v>
+        <v>0.0779727514037015</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.06305419008778301</v>
+        <v>0.03356696213442806</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE4" t="n">
-        <v>109.9333333333333</v>
+        <v>219.8666666666667</v>
       </c>
       <c r="AF4" t="n">
-        <v>16.7279769324616</v>
+        <v>26.1383404502086</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.1674242900861033</v>
+        <v>0.1234147275116123</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.1087532956261173</v>
+        <v>0.04807358790296923</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AK4" t="n">
-        <v>104.1333333333333</v>
+        <v>208.2666666666667</v>
       </c>
       <c r="AL4" t="n">
         <v>101.776219293998</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.1664196509681836</v>
+        <v>0.0780079423509748</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.05510490924496336</v>
+        <v>0.0302820104739101</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -891,121 +891,121 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.897887857284426</v>
+        <v>12.583061891297</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1603405719537761</v>
+        <v>0.07943758473524903</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08532826013119077</v>
+        <v>0.04726819347520286</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>101.9</v>
+        <v>203.8</v>
       </c>
       <c r="H5" t="n">
-        <v>73.36665052560107</v>
+        <v>86.33687993475564</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2086065399541217</v>
+        <v>0.09898862098827198</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08028011776773106</v>
+        <v>0.04557676494738867</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M5" t="n">
-        <v>358.1</v>
+        <v>716.2</v>
       </c>
       <c r="N5" t="n">
-        <v>20.8238214079352</v>
+        <v>28.53912060695032</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1902543564673508</v>
+        <v>0.09237626361285096</v>
       </c>
       <c r="P5" t="n">
-        <v>0.08582103310416518</v>
+        <v>0.04459290803261738</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
+        <v>52</v>
+      </c>
+      <c r="S5" t="n">
+        <v>303.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>22.3286866061602</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.0951606489039685</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.04954818402806949</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>238.1333333333333</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>12.34844341057875</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.08729723725469034</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.0534179774986013</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>41</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>156.5333333333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>26.90398797604762</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.1318695627824417</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.06798940844820194</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>46</v>
       </c>
-      <c r="S5" t="n">
-        <v>151.6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>11.69909809201082</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1763598618683644</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.1106626878317186</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>48</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>119.0666666666667</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.056849236161172</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.1953665197183859</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.09256332358369591</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>37</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>78.26666666666667</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>12.18162446220907</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.1962377614457268</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.1027918669273066</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>40</v>
-      </c>
       <c r="AK5" t="n">
-        <v>111.0333333333333</v>
+        <v>222.0666666666667</v>
       </c>
       <c r="AL5" t="n">
         <v>118.6162571082527</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.2163998495352521</v>
+        <v>0.100717465485699</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.08260124783211797</v>
+        <v>0.04300761593322877</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1027,121 +1027,121 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.429678198603778</v>
+        <v>6.242215645324368</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2214999353912628</v>
+        <v>0.1139815495006231</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8165137285929931</v>
+        <v>0.03971315624537648</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G6" t="n">
-        <v>72.5</v>
+        <v>145</v>
       </c>
       <c r="H6" t="n">
-        <v>91.10363616619249</v>
+        <v>101.4002124727247</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2389009620108258</v>
+        <v>0.1109404826679458</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1066461139331551</v>
+        <v>0.06058193994203658</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M6" t="n">
-        <v>386.6</v>
+        <v>773.2</v>
       </c>
       <c r="N6" t="n">
-        <v>15.51601693870122</v>
+        <v>23.93938704069906</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2277433152235261</v>
+        <v>0.1141085599162029</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1093759643924781</v>
+        <v>0.05671534183028799</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S6" t="n">
-        <v>103.9</v>
+        <v>207.8</v>
       </c>
       <c r="T6" t="n">
-        <v>14.3039698611145</v>
+        <v>23.59068567335524</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1962182067073501</v>
+        <v>0.1010546664509893</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1242201107219285</v>
+        <v>0.05346520571374424</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Y6" t="n">
-        <v>136.7</v>
+        <v>273.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.2392198648337</v>
+        <v>24.74978023178979</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2326279690547355</v>
+        <v>0.1026806067440462</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.129589889625091</v>
+        <v>0.05595917694367464</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="AE6" t="n">
-        <v>103.3333333333333</v>
+        <v>206.6666666666667</v>
       </c>
       <c r="AF6" t="n">
-        <v>8.196242963822577</v>
+        <v>21.59710872559104</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.2523938404091896</v>
+        <v>0.1270676127897696</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.124130577068717</v>
+        <v>0.07749554091506092</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="AK6" t="n">
-        <v>115.1333333333333</v>
+        <v>230.2666666666667</v>
       </c>
       <c r="AL6" t="n">
         <v>142.6761055675479</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.2453407532664488</v>
+        <v>0.1150131695712198</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.09217621416074528</v>
+        <v>0.05393346503512758</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1163,121 +1163,121 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.887361770984975</v>
+        <v>9.334249059398754</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1536257458172552</v>
+        <v>0.07662185191834713</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0594380607072011</v>
+        <v>0.03804943300195249</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>102.1</v>
+        <v>204.2</v>
       </c>
       <c r="H7" t="n">
-        <v>93.77199763381286</v>
+        <v>95.05103438392274</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2544526063606542</v>
+        <v>0.1146068946666164</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1071552917355867</v>
+        <v>0.05811593053377851</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M7" t="n">
-        <v>356.3333333333333</v>
+        <v>712.6666666666666</v>
       </c>
       <c r="N7" t="n">
-        <v>19.07567604384313</v>
+        <v>24.40680497678061</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2214175511244321</v>
+        <v>0.1179961770552783</v>
       </c>
       <c r="P7" t="n">
-        <v>0.09691870987658117</v>
+        <v>0.0543733780054616</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
+        <v>58</v>
+      </c>
+      <c r="S7" t="n">
+        <v>240.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>21.39027190870748</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.08802115836011429</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.06071456997108626</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
         <v>54</v>
       </c>
-      <c r="S7" t="n">
-        <v>120.1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>13.20507750177276</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.1876208810327632</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.08263779481704492</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>49</v>
-      </c>
       <c r="Y7" t="n">
-        <v>116.7333333333333</v>
+        <v>233.4666666666667</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.49789694912132</v>
+        <v>29.47250457724286</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2567879939539848</v>
+        <v>0.118037093128484</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.08546837902918596</v>
+        <v>0.06360084566185094</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="AE7" t="n">
-        <v>113.4333333333333</v>
+        <v>226.8666666666667</v>
       </c>
       <c r="AF7" t="n">
-        <v>9.036939763052976</v>
+        <v>26.73433803973026</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.239633326855345</v>
+        <v>0.1270415871944257</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.124566026893491</v>
+        <v>0.07678795297543853</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="AK7" t="n">
-        <v>108.1</v>
+        <v>216.2</v>
       </c>
       <c r="AL7" t="n">
         <v>129.855614792095</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.2368807266397193</v>
+        <v>0.112785552121465</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.08804178472974411</v>
+        <v>0.04914850624491818</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1299,124 +1299,124 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.599431234280951</v>
+        <v>5.963644269048829</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1343455385351136</v>
+        <v>0.07187961311840602</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03587457796986676</v>
+        <v>0.03229081981237343</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
-        <v>83.96666666666667</v>
+        <v>167.9333333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>70.97637606186738</v>
+        <v>73.6523271916205</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1765451916577977</v>
+        <v>0.08273184002901196</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07505983228256628</v>
+        <v>0.03678499794982104</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="L8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M8" t="n">
-        <v>375.5333333333334</v>
+        <v>751.0666666666667</v>
       </c>
       <c r="N8" t="n">
-        <v>17.7336458017406</v>
+        <v>21.76020511279709</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1724177755120934</v>
+        <v>0.08897697553872716</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0770236136565503</v>
+        <v>0.032960644572614</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="S8" t="n">
-        <v>116.4666666666667</v>
+        <v>232.9333333333333</v>
       </c>
       <c r="T8" t="n">
-        <v>17.77276951027844</v>
+        <v>21.85886411414507</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1465276614678868</v>
+        <v>0.07455259613363051</v>
       </c>
       <c r="V8" t="n">
-        <v>0.08624001904141024</v>
+        <v>0.03414683679138096</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Y8" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.994475753396696</v>
+        <v>13.51241157533123</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.1556280230898913</v>
+        <v>0.07877656667167739</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.06542817375034576</v>
+        <v>0.0355111470439535</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AE8" t="n">
-        <v>90.26666666666667</v>
+        <v>180.5333333333333</v>
       </c>
       <c r="AF8" t="n">
-        <v>16.2432615254755</v>
+        <v>21.40789380546459</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.1800761675810571</v>
+        <v>0.0879523274589008</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0917633277034243</v>
+        <v>0.04897832655586759</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK8" t="n">
-        <v>122.7333333333333</v>
+        <v>245.4666666666667</v>
       </c>
       <c r="AL8" t="n">
         <v>93.43753832522802</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.175815877206305</v>
+        <v>0.08355957749099607</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.06264102414521333</v>
+        <v>0.03346745914984361</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.2</v>
+        <v>6.933333333333334</v>
       </c>
       <c r="AP8" t="n">
         <v>403</v>
@@ -1435,124 +1435,124 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.465664376785313</v>
+        <v>3.356654694021463</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1443272975395256</v>
+        <v>0.07885607470479868</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0532884886193829</v>
+        <v>0.04084752978753484</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F9" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G9" t="n">
-        <v>60.16666666666666</v>
+        <v>120.3333333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>117.1965566684043</v>
+        <v>127.0615811678257</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2667755426500108</v>
+        <v>0.1256824645567698</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1148863536555729</v>
+        <v>0.06181175248432808</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="M9" t="n">
-        <v>398.8</v>
+        <v>797.6</v>
       </c>
       <c r="N9" t="n">
-        <v>25.86656260258239</v>
+        <v>37.9625427932023</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2537965089070776</v>
+        <v>0.1265713737032565</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1112269406150996</v>
+        <v>0.06231684371447582</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S9" t="n">
-        <v>126.0333333333333</v>
+        <v>252.0666666666667</v>
       </c>
       <c r="T9" t="n">
-        <v>6.309589198528514</v>
+        <v>16.46722415258514</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1931002083883422</v>
+        <v>0.1084682159192892</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1210301223232374</v>
+        <v>0.06653773641653617</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
+        <v>62</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>187.4666666666667</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>24.28562640651845</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.1139905525119356</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.08718910762751661</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
         <v>55</v>
       </c>
-      <c r="Y9" t="n">
-        <v>93.73333333333333</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>9.629565786568993</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.2279078267221475</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.1196841504608492</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>50</v>
-      </c>
       <c r="AE9" t="n">
-        <v>102.3333333333333</v>
+        <v>204.6666666666667</v>
       </c>
       <c r="AF9" t="n">
-        <v>23.56916315644433</v>
+        <v>33.67206435190314</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.3096728237497984</v>
+        <v>0.1352181399415543</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.1839398346395203</v>
+        <v>0.07987774536244625</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="AK9" t="n">
-        <v>136.8</v>
+        <v>273.6</v>
       </c>
       <c r="AL9" t="n">
         <v>166.0857229838505</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.2752412261710493</v>
+        <v>0.1308183054032868</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.1161167977027371</v>
+        <v>0.05799563874627456</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AP9" t="n">
         <v>407</v>
@@ -1571,121 +1571,121 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.518155638657689</v>
+        <v>13.89642268892705</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1388378166408471</v>
+        <v>0.06863531593902363</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05941659318499212</v>
+        <v>0.03105971621407762</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>141.2</v>
+        <v>282.4</v>
       </c>
       <c r="H10" t="n">
-        <v>55.12365862383209</v>
+        <v>59.00632596139268</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1689299468638804</v>
+        <v>0.07910546776139189</v>
       </c>
       <c r="J10" t="n">
-        <v>0.07074548786368944</v>
+        <v>0.03585221157020555</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="M10" t="n">
-        <v>324.6</v>
+        <v>649.2</v>
       </c>
       <c r="N10" t="n">
-        <v>16.50789723045635</v>
+        <v>22.68957374620598</v>
       </c>
       <c r="O10" t="n">
-        <v>0.153814037353883</v>
+        <v>0.08191268961477191</v>
       </c>
       <c r="P10" t="n">
-        <v>0.06131998187326531</v>
+        <v>0.03409825132694607</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="S10" t="n">
-        <v>131.3333333333333</v>
+        <v>262.6666666666667</v>
       </c>
       <c r="T10" t="n">
-        <v>16.17798572590725</v>
+        <v>21.98738749782327</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1319101406246343</v>
+        <v>0.06692140067509135</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1499883540280666</v>
+        <v>0.03226891658131851</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="Y10" t="n">
-        <v>143.7333333333333</v>
+        <v>287.4666666666666</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.686961587072124</v>
+        <v>14.43328569485597</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.171073446299308</v>
+        <v>0.08461018211379596</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.05415162172590133</v>
+        <v>0.03769686429607758</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AE10" t="n">
-        <v>76.2</v>
+        <v>152.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>15.88649895125127</v>
+        <v>18.21749912482592</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.168091187921446</v>
+        <v>0.08069678077767677</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0702117224109074</v>
+        <v>0.03982913500072222</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>114.5</v>
+        <v>229</v>
       </c>
       <c r="AL10" t="n">
         <v>92.25802557513893</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.1741115292603993</v>
+        <v>0.08272811954728237</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.06239646016858125</v>
+        <v>0.03009931309549918</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -1707,121 +1707,121 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.941548781626226</v>
+        <v>4.928107047819315</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1727690588914225</v>
+        <v>0.08910653685073019</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05534777245027306</v>
+        <v>0.04266060064120192</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G11" t="n">
-        <v>78.33333333333333</v>
+        <v>156.6666666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>90.58573365272413</v>
+        <v>95.78768678066369</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2149099234792037</v>
+        <v>0.1029890172273745</v>
       </c>
       <c r="J11" t="n">
-        <v>0.09180911715412125</v>
+        <v>0.04903170661580854</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
-        <v>382.4</v>
+        <v>764.8</v>
       </c>
       <c r="N11" t="n">
-        <v>13.54477174804428</v>
+        <v>25.44650054398828</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2005597486767583</v>
+        <v>0.1053299862502434</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1020755497541687</v>
+        <v>0.04082996204595144</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="S11" t="n">
-        <v>130.8333333333333</v>
+        <v>261.6666666666667</v>
       </c>
       <c r="T11" t="n">
-        <v>8.871597527296213</v>
+        <v>18.78149465806359</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1866308333272479</v>
+        <v>0.09653428972483361</v>
       </c>
       <c r="V11" t="n">
-        <v>0.08889547855643988</v>
+        <v>0.04841356270313039</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="Y11" t="n">
-        <v>113.5666666666667</v>
+        <v>227.1333333333333</v>
       </c>
       <c r="Z11" t="n">
-        <v>15.53187346119699</v>
+        <v>24.33738426037921</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.2011990918227136</v>
+        <v>0.1000283966102915</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.1237669660894551</v>
+        <v>0.05462019595247596</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="AE11" t="n">
-        <v>115.9</v>
+        <v>231.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>14.5998650998037</v>
+        <v>25.06249754369886</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.3239747597437524</v>
+        <v>0.1349831962832939</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.1897138820063286</v>
+        <v>0.06698097392124268</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="AK11" t="n">
-        <v>100.4333333333333</v>
+        <v>200.8666666666667</v>
       </c>
       <c r="AL11" t="n">
         <v>126.7697939109799</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.2195538030687252</v>
+        <v>0.106868454831211</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.08074059639346759</v>
+        <v>0.04509203250682636</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -1843,124 +1843,124 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.607719523181491</v>
+        <v>11.57644449956111</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1335711899289542</v>
+        <v>0.08389747543089834</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08207219942335012</v>
+        <v>0.03806489101348395</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G12" t="n">
-        <v>115.3</v>
+        <v>230.6</v>
       </c>
       <c r="H12" t="n">
-        <v>64.290688284059</v>
+        <v>75.14961322121977</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1944837084016628</v>
+        <v>0.09242411574338537</v>
       </c>
       <c r="J12" t="n">
-        <v>0.08208543148068231</v>
+        <v>0.04605139975844426</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>5.066666666666666</v>
       </c>
       <c r="L12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="M12" t="n">
-        <v>345.8</v>
+        <v>691.6</v>
       </c>
       <c r="N12" t="n">
-        <v>11.11856330519697</v>
+        <v>17.82291320623315</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1904220469677662</v>
+        <v>0.08979639520790243</v>
       </c>
       <c r="P12" t="n">
-        <v>0.06543620612669362</v>
+        <v>0.02890230259378759</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="S12" t="n">
-        <v>108.0666666666667</v>
+        <v>216.1333333333333</v>
       </c>
       <c r="T12" t="n">
-        <v>16.00122773606612</v>
+        <v>24.10616647240366</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1827392488769917</v>
+        <v>0.0833307486293882</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0813837885723304</v>
+        <v>0.04827030564409712</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Y12" t="n">
-        <v>132.6333333333333</v>
+        <v>265.2666666666667</v>
       </c>
       <c r="Z12" t="n">
-        <v>11.94355545829791</v>
+        <v>16.01027863924803</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1698506643048633</v>
+        <v>0.08029630758850417</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.07302156365976001</v>
+        <v>0.03987084893008641</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="AE12" t="n">
-        <v>99.7</v>
+        <v>199.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>13.83800638912355</v>
+        <v>20.36495696093699</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.1780699845685047</v>
+        <v>0.09304294805829302</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.08515926665918344</v>
+        <v>0.05061508270274991</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="AK12" t="n">
-        <v>120.7</v>
+        <v>241.4</v>
       </c>
       <c r="AL12" t="n">
         <v>109.2290231104454</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.1995174560896437</v>
+        <v>0.09320209675241686</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.05952029274900822</v>
+        <v>0.03535317955028466</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AP12" t="n">
         <v>443</v>
@@ -1979,124 +1979,124 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.539383500802052</v>
+        <v>9.78993085614497</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1629015692717693</v>
+        <v>0.07925493951418315</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08435330907067685</v>
+        <v>0.04428912822372735</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G13" t="n">
-        <v>96.03333333333333</v>
+        <v>192.0666666666667</v>
       </c>
       <c r="H13" t="n">
-        <v>92.92997253410113</v>
+        <v>97.84279135203327</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2350522602731407</v>
+        <v>0.1081364043833067</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1189041781939572</v>
+        <v>0.05389663769675946</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="L13" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="M13" t="n">
-        <v>366.9666666666666</v>
+        <v>733.9333333333333</v>
       </c>
       <c r="N13" t="n">
-        <v>11.31998059958758</v>
+        <v>28.02329767419196</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1873755954116368</v>
+        <v>0.1092158558648715</v>
       </c>
       <c r="P13" t="n">
-        <v>0.06297697211296154</v>
+        <v>0.05391477343263048</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="S13" t="n">
-        <v>135.4666666666667</v>
+        <v>270.9333333333333</v>
       </c>
       <c r="T13" t="n">
-        <v>7.686156333208896</v>
+        <v>19.06128022518705</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1733929908294148</v>
+        <v>0.0975878054408678</v>
       </c>
       <c r="V13" t="n">
-        <v>0.07978960071181755</v>
+        <v>0.06084996123175961</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="Y13" t="n">
-        <v>106.0666666666667</v>
+        <v>212.1333333333333</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.73209603307452</v>
+        <v>26.56593599111806</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.203601064200552</v>
+        <v>0.09887363189629998</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1032264243125096</v>
+        <v>0.05405113742726458</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AE13" t="n">
-        <v>128.2</v>
+        <v>256.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>7.495449083700777</v>
+        <v>16.05899575741524</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.1835097907122608</v>
+        <v>0.09701879409563599</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.1108586229806441</v>
+        <v>0.05779304165064549</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="AJ13" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AK13" t="n">
-        <v>93.26666666666667</v>
+        <v>186.5333333333333</v>
       </c>
       <c r="AL13" t="n">
         <v>133.6381287346002</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.2358284653950989</v>
+        <v>0.1073999409927454</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.08458199632669028</v>
+        <v>0.04968058632947903</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="AP13" t="n">
         <v>444</v>
@@ -2115,121 +2115,121 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.194195690217924</v>
+        <v>6.773081727819254</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1555317454465964</v>
+        <v>0.07847340554864969</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0671704048262233</v>
+        <v>0.0313216106456788</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>92.83333333333333</v>
+        <v>185.6666666666667</v>
       </c>
       <c r="H14" t="n">
-        <v>86.34317062851659</v>
+        <v>83.87090614710247</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2054420443436103</v>
+        <v>0.09704563959200706</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1009219358818604</v>
+        <v>0.04773826443753383</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="M14" t="n">
-        <v>367.1666666666667</v>
+        <v>734.3333333333334</v>
       </c>
       <c r="N14" t="n">
-        <v>18.8190557751175</v>
+        <v>29.7070090483564</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1786001207680085</v>
+        <v>0.0915798913128604</v>
       </c>
       <c r="P14" t="n">
-        <v>0.09182673144634032</v>
+        <v>0.04715204464135725</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="S14" t="n">
-        <v>146.4666666666667</v>
+        <v>292.9333333333333</v>
       </c>
       <c r="T14" t="n">
-        <v>7.455324421434101</v>
+        <v>24.20347309242564</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1718148319656647</v>
+        <v>0.08536973847181123</v>
       </c>
       <c r="V14" t="n">
-        <v>0.07270035693752203</v>
+        <v>0.07870717159338686</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="Y14" t="n">
-        <v>115.2</v>
+        <v>230.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.439807555026185</v>
+        <v>13.13903397340976</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.202288448798124</v>
+        <v>0.08964428910460623</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.1233858987823817</v>
+        <v>0.04169419680132452</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="AE14" t="n">
-        <v>93.03333333333333</v>
+        <v>186.0666666666667</v>
       </c>
       <c r="AF14" t="n">
-        <v>5.24987803852294</v>
+        <v>16.76684100282763</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.1745436881897641</v>
+        <v>0.09304439281773637</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.1489958326608812</v>
+        <v>0.05001764196915588</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="AK14" t="n">
-        <v>105.2666666666667</v>
+        <v>210.5333333333333</v>
       </c>
       <c r="AL14" t="n">
         <v>120.7250741237556</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.2081646558205516</v>
+        <v>0.1001794215568345</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0855406659449896</v>
+        <v>0.04575440009339848</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -2251,124 +2251,124 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.419434797869007</v>
+        <v>9.241509626379194</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1028492992620722</v>
+        <v>0.05726252863407694</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03869733747457157</v>
+        <v>0.01860514878459645</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>7.133333333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
-        <v>117</v>
+        <v>234</v>
       </c>
       <c r="H15" t="n">
-        <v>75.20503803449822</v>
+        <v>83.19548034220132</v>
       </c>
       <c r="I15" t="n">
-        <v>0.219077030706696</v>
+        <v>0.1033127042750413</v>
       </c>
       <c r="J15" t="n">
-        <v>0.08566858515927206</v>
+        <v>0.04577846655615431</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L15" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M15" t="n">
-        <v>342.5666666666667</v>
+        <v>685.1333333333333</v>
       </c>
       <c r="N15" t="n">
-        <v>7.833792188546971</v>
+        <v>18.94378817347977</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1676584997654706</v>
+        <v>0.103418910612905</v>
       </c>
       <c r="P15" t="n">
-        <v>0.05737460870851663</v>
+        <v>0.04378689135133181</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R15" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="S15" t="n">
-        <v>105</v>
+        <v>210</v>
       </c>
       <c r="T15" t="n">
-        <v>9.754515426931075</v>
+        <v>17.37264089896223</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1406063000866873</v>
+        <v>0.0768099648319004</v>
       </c>
       <c r="V15" t="n">
-        <v>0.04638690058079356</v>
+        <v>0.03206106775413697</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="X15" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="Y15" t="n">
-        <v>121.6666666666667</v>
+        <v>243.3333333333333</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.8036322961428</v>
+        <v>22.01896318308965</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.1885418543896103</v>
+        <v>0.09387451845501274</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.1131445848807363</v>
+        <v>0.04676849394253055</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AE15" t="n">
-        <v>115.0666666666667</v>
+        <v>230.1333333333333</v>
       </c>
       <c r="AF15" t="n">
-        <v>13.51746183386302</v>
+        <v>28.70890771109931</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.174149473079796</v>
+        <v>0.1218629164709354</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.07451409366053154</v>
+        <v>0.08091317775373884</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AK15" t="n">
-        <v>117.8</v>
+        <v>235.6</v>
       </c>
       <c r="AL15" t="n">
         <v>110.5123604293532</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.2022495141663566</v>
+        <v>0.09238011355232284</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.06796628073952549</v>
+        <v>0.03713916498393843</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="AP15" t="n">
         <v>448</v>
@@ -2387,103 +2387,103 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.972809076871483</v>
+        <v>7.26702925752846</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1838507872003829</v>
+        <v>0.08729821608677202</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1099336795504874</v>
+        <v>0.03853334047484728</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G16" t="n">
-        <v>83.03333333333333</v>
+        <v>166.0666666666667</v>
       </c>
       <c r="H16" t="n">
-        <v>67.03029403820992</v>
+        <v>75.55346972603674</v>
       </c>
       <c r="I16" t="n">
-        <v>0.177625927448693</v>
+        <v>0.08338293310548285</v>
       </c>
       <c r="J16" t="n">
-        <v>0.06999590243452315</v>
+        <v>0.03253860974675814</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M16" t="n">
-        <v>377.1</v>
+        <v>754.2</v>
       </c>
       <c r="N16" t="n">
-        <v>20.57997313924546</v>
+        <v>23.50722681911828</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1717290441221354</v>
+        <v>0.08793578712233711</v>
       </c>
       <c r="P16" t="n">
-        <v>0.05333414461231367</v>
+        <v>0.0286924184640266</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="S16" t="n">
-        <v>134.5666666666667</v>
+        <v>269.1333333333333</v>
       </c>
       <c r="T16" t="n">
-        <v>17.43415397024313</v>
+        <v>22.07597920433532</v>
       </c>
       <c r="U16" t="n">
-        <v>0.153222749164912</v>
+        <v>0.07537146861404458</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0964329220200446</v>
+        <v>0.02732459851550194</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Y16" t="n">
-        <v>124.4</v>
+        <v>248.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.59857852832572</v>
+        <v>19.10275332114886</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.1755106871051702</v>
+        <v>0.08620349706339003</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.180482867519541</v>
+        <v>0.04834459455560886</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
-        <v>83.3</v>
+        <v>166.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>17.88512186723031</v>
+        <v>21.13473063773167</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.1625089205224268</v>
+        <v>0.08178497345731554</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.05657622846101044</v>
+        <v>0.03053752894275012</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2492,16 +2492,16 @@
         <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>117.7666666666667</v>
+        <v>235.5333333333333</v>
       </c>
       <c r="AL16" t="n">
         <v>96.80117319580734</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.1765262083018533</v>
+        <v>0.0854768248503614</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.05596572008350081</v>
+        <v>0.0286069197689606</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -2523,124 +2523,124 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1.193410192669651</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.09738634372436861</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.03161151849158203</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>34.1</v>
+        <v>68.2</v>
       </c>
       <c r="H17" t="n">
-        <v>109.2149773859155</v>
+        <v>118.6081920045214</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2042948073007448</v>
+        <v>0.09738985582809886</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08435251128115664</v>
+        <v>0.04368029132169254</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="L17" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M17" t="n">
-        <v>429.7666666666667</v>
+        <v>859.5333333333333</v>
       </c>
       <c r="N17" t="n">
-        <v>9.425219806332541</v>
+        <v>17.00931384031415</v>
       </c>
       <c r="O17" t="n">
-        <v>0.207979429822945</v>
+        <v>0.1019361667181171</v>
       </c>
       <c r="P17" t="n">
-        <v>0.05455117220284426</v>
+        <v>0.05051445982457931</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S17" t="n">
-        <v>87.3</v>
+        <v>174.6</v>
       </c>
       <c r="T17" t="n">
-        <v>11.7086833138259</v>
+        <v>18.57275941365556</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1504729644365826</v>
+        <v>0.080860487366252</v>
       </c>
       <c r="V17" t="n">
-        <v>0.05888846293392982</v>
+        <v>0.03930258072295215</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Y17" t="n">
-        <v>113.4</v>
+        <v>226.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.11262009365132</v>
+        <v>21.30140868522361</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.2015835405108791</v>
+        <v>0.09879743020541479</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.08815779227747515</v>
+        <v>0.05323573089186858</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE17" t="n">
-        <v>98.46666666666667</v>
+        <v>196.9333333333333</v>
       </c>
       <c r="AF17" t="n">
-        <v>25.0948060504394</v>
+        <v>31.41413187316643</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.2092177388424256</v>
+        <v>0.09049404132950084</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.1029983008959158</v>
+        <v>0.0512699171306135</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="AJ17" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="AK17" t="n">
-        <v>164.7</v>
+        <v>329.4</v>
       </c>
       <c r="AL17" t="n">
         <v>141.1779461143055</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.2099538681950791</v>
+        <v>0.1010651169725398</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.08364943923688828</v>
+        <v>0.03988794305644261</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="AP17" t="n">
         <v>461</v>
@@ -2659,13 +2659,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.45278978651704</v>
+        <v>9.441281111354009</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1792853149841262</v>
+        <v>0.09115280880409395</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05567199428203411</v>
+        <v>0.0381846206414235</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -2674,109 +2674,109 @@
         <v>73</v>
       </c>
       <c r="G18" t="n">
-        <v>90.16666666666667</v>
+        <v>180.3333333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>92.7947120363247</v>
+        <v>99.64526983465785</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2253157468065259</v>
+        <v>0.1045672972934378</v>
       </c>
       <c r="J18" t="n">
-        <v>0.08842540186276067</v>
+        <v>0.04908291887437882</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="L18" t="n">
         <v>71</v>
       </c>
       <c r="M18" t="n">
-        <v>371.4333333333333</v>
+        <v>742.8666666666667</v>
       </c>
       <c r="N18" t="n">
-        <v>9.968098625977538</v>
+        <v>25.35973058365388</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2606109970504856</v>
+        <v>0.1199844251130775</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2040339074839625</v>
+        <v>0.07950296561305818</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S18" t="n">
-        <v>97.03333333333333</v>
+        <v>194.0666666666667</v>
       </c>
       <c r="T18" t="n">
-        <v>9.052669826113929</v>
+        <v>17.52798751344172</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1863041523169645</v>
+        <v>0.09250941061454838</v>
       </c>
       <c r="V18" t="n">
-        <v>0.09894297603913248</v>
+        <v>0.03963561379364597</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Y18" t="n">
-        <v>94.66666666666667</v>
+        <v>189.3333333333333</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.65623899559518</v>
+        <v>30.11409280193253</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.2091650574586623</v>
+        <v>0.09408080698759715</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.07457131732176361</v>
+        <v>0.04739783422873411</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="AE18" t="n">
-        <v>134.4333333333333</v>
+        <v>268.8666666666667</v>
       </c>
       <c r="AF18" t="n">
-        <v>14.56364858899031</v>
+        <v>23.83871227501834</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.1735701966147993</v>
+        <v>0.0990887556842187</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.1071929939825683</v>
+        <v>0.05834752942487296</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AK18" t="n">
-        <v>135.4</v>
+        <v>270.8</v>
       </c>
       <c r="AL18" t="n">
         <v>124.9771126375922</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.2293794186830592</v>
+        <v>0.1036409043961886</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.0751906015912846</v>
+        <v>0.03980714273160402</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="AP18" t="n">
         <v>463</v>
@@ -2795,121 +2795,121 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.231435812471977</v>
+        <v>7.077540972169516</v>
       </c>
       <c r="C19" t="n">
-        <v>0.08386863268840551</v>
+        <v>0.07276742687052203</v>
       </c>
       <c r="D19" t="n">
-        <v>0.05203562775882131</v>
+        <v>0.02757522234269768</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G19" t="n">
-        <v>82.59999999999999</v>
+        <v>165.2</v>
       </c>
       <c r="H19" t="n">
-        <v>87.72404736932168</v>
+        <v>96.16986202468267</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2263283767700721</v>
+        <v>0.1065966477577211</v>
       </c>
       <c r="J19" t="n">
-        <v>0.09496918440216522</v>
+        <v>0.04749596969009969</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M19" t="n">
-        <v>377.7333333333333</v>
+        <v>755.4666666666667</v>
       </c>
       <c r="N19" t="n">
-        <v>6.009462597471349</v>
+        <v>15.56440043458382</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2029596849668311</v>
+        <v>0.1145525201676869</v>
       </c>
       <c r="P19" t="n">
-        <v>0.06713211540589843</v>
+        <v>0.03981550762287249</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="S19" t="n">
-        <v>77.33333333333333</v>
+        <v>154.6666666666667</v>
       </c>
       <c r="T19" t="n">
-        <v>13.04438699817716</v>
+        <v>21.92594671222907</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1751284728985872</v>
+        <v>0.08870036986039623</v>
       </c>
       <c r="V19" t="n">
-        <v>0.06666476595472205</v>
+        <v>0.0463191291475451</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Y19" t="n">
-        <v>122.0333333333333</v>
+        <v>244.0666666666667</v>
       </c>
       <c r="Z19" t="n">
-        <v>10.33363537769223</v>
+        <v>19.89742010478567</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.2120673511823132</v>
+        <v>0.0999893621263441</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.177126941400094</v>
+        <v>0.04759769306166294</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AE19" t="n">
-        <v>111.3333333333333</v>
+        <v>222.6666666666667</v>
       </c>
       <c r="AF19" t="n">
-        <v>18.30042672224592</v>
+        <v>29.26281523942326</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.2107367230827403</v>
+        <v>0.09687149814816073</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.09977571444169094</v>
+        <v>0.05469822297247356</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="AK19" t="n">
-        <v>149.6333333333333</v>
+        <v>299.2666666666667</v>
       </c>
       <c r="AL19" t="n">
         <v>122.8740434437623</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.2195643307131504</v>
+        <v>0.1013714129167991</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.07808696992095765</v>
+        <v>0.04068005681141057</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
